--- a/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T10:06:59+00:00</t>
+    <t>2026-08-20T14:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1285,7 +1285,7 @@
     <t>Body site where vaccine was administered.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260619134041</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-approach-site-code-cisis|20260716085851</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1306,7 +1306,7 @@
     <t>The path by which the vaccine product is taken into the body.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-immunization-route-code-cisis|20260716085852</t>
   </si>
   <si>
     <t>RXR-1</t>
@@ -1731,7 +1731,7 @@
     <t>One possible path to achieve presumed immunity against a disease - within the context of an authority.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdministrationImmunizationCode-cisis|20260716085853</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.authority</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T14:37:13+00:00</t>
+    <t>2026-08-25T08:25:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T08:25:54+00:00</t>
+    <t>2026-08-25T13:09:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:09:33+00:00</t>
+    <t>2026-08-25T13:40:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:40:20+00:00</t>
+    <t>2026-08-25T14:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T14:52:49+00:00</t>
+    <t>2026-08-26T13:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:43:53+00:00</t>
+    <t>2026-08-26T14:38:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T14:38:07+00:00</t>
+    <t>2026-08-27T07:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
